--- a/fixtures/jeju/timetables/bis/raw/405145.xlsx
+++ b/fixtures/jeju/timetables/bis/raw/405145.xlsx
@@ -6,10 +6,10 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="357-1 월평-시청-터미널-신제주R-한라병원-수산" r:id="rId3" sheetId="1"/>
-    <sheet name="357-1 하귀-한라병원-신제주R-터미널-시청-월평" r:id="rId4" sheetId="2"/>
-    <sheet name="358-1 월평-시청-터미널-신제주R-한라병원-수산" r:id="rId5" sheetId="3"/>
-    <sheet name="358-1 하귀-한라병원-신제주R-터미널-시청-월평" r:id="rId6" sheetId="4"/>
+    <sheet name="357-1 하귀-한라병원-신제주R-터미널-시청-월평" r:id="rId3" sheetId="1"/>
+    <sheet name="357-1 월평-시청-터미널-신제주R-한라병원-수산" r:id="rId4" sheetId="2"/>
+    <sheet name="358-1 하귀-한라병원-신제주R-터미널-시청-월평" r:id="rId5" sheetId="3"/>
+    <sheet name="358-1 월평-시청-터미널-신제주R-한라병원-수산" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
@@ -23,48 +23,116 @@
     <t>노선번호</t>
   </si>
   <si>
+    <t>수산(하귀)</t>
+  </si>
+  <si>
+    <t>하귀휴먼시아</t>
+  </si>
+  <si>
+    <t>외도부영</t>
+  </si>
+  <si>
+    <t>한라병원</t>
+  </si>
+  <si>
+    <t>제주도청(신제주로타리)</t>
+  </si>
+  <si>
+    <t>터미널</t>
+  </si>
+  <si>
+    <t>보건소</t>
+  </si>
+  <si>
+    <t>법원</t>
+  </si>
+  <si>
     <t>월평</t>
   </si>
   <si>
-    <t>법원</t>
+    <t>비고</t>
+  </si>
+  <si>
+    <t>357-1번</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>06:56</t>
+  </si>
+  <si>
+    <t>07:06</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:36</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>토,공휴일방학기간운행 안함</t>
+  </si>
+  <si>
+    <t>358-1번</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>07:16</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>08:03</t>
+  </si>
+  <si>
+    <t>08:24</t>
+  </si>
+  <si>
+    <t>수요맞춤형 357-1번,358-1번</t>
+  </si>
+  <si>
+    <t>[357-1번]  하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트-내도동-이호2동(대동마을)-제주민속오일시장 -월랑초등학교-한라병원-수협제주도지회-제주도청(신제주로터리)-세기아파트-보건소-(이도초등학교)-법원-제주중앙여자고등학교-아라초등학교-신성여자중고등학교-중앙고등학교-월평
+[358-1번]  하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트-내도동-이호2동(대동마을)-제주민속오일시장-월랑초등학교-한라병원-수협제주도지회-제주도청(신제주로터리)-버스터미널-제주시청-제주중앙여자고등학교-아라초등학교-신성여자중고등학교-중앙고등학교-월평
+※ 토,공휴일,방학기간 운행 안함</t>
+  </si>
+  <si>
+    <t>수산(하귀)→제주도청→월평</t>
+  </si>
+  <si>
+    <t>삼영교통(064-713-7000)</t>
+  </si>
+  <si>
+    <t>(시행일 : 2024.8.1.)</t>
   </si>
   <si>
     <t>이도초등학교</t>
   </si>
   <si>
-    <t>보건소</t>
-  </si>
-  <si>
-    <t>터미널</t>
-  </si>
-  <si>
-    <t>제주도청(신제주로타리)</t>
-  </si>
-  <si>
-    <t>한라병원</t>
-  </si>
-  <si>
-    <t>외도부영</t>
-  </si>
-  <si>
-    <t>하귀휴먼시아</t>
-  </si>
-  <si>
-    <t>수산(하귀)</t>
-  </si>
-  <si>
-    <t>비고</t>
-  </si>
-  <si>
-    <t>357-1번</t>
-  </si>
-  <si>
     <t>16:08</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
     <t>16:30</t>
   </si>
   <si>
@@ -86,12 +154,6 @@
     <t>17:42</t>
   </si>
   <si>
-    <t>토,공휴일방학기간운행 안함</t>
-  </si>
-  <si>
-    <t>358-1번</t>
-  </si>
-  <si>
     <t>17:03</t>
   </si>
   <si>
@@ -150,9 +212,6 @@
   </si>
   <si>
     <t>19:24</t>
-  </si>
-  <si>
-    <t>수요맞춤형 357-1번,358-1번</t>
   </si>
   <si>
     <t>[357-1번]  월평-중앙고등학교-신성여자중고등학교-아라초등학교-제주중앙여자고등학교-이도초등학교-보건소-세기아파트-제주도청(신제주로터리)-수협제주도지회-한라병원-월랑초등학교-제주민속오일시장-이호이동(대동마을)-내도동-외도부영1,2차아파트-하귀휴먼시아1,2단지-하귀초등학교-하귀(수산)
@@ -164,65 +223,6 @@
   </si>
   <si>
     <t>관광지순환버스(064-746-7310)</t>
-  </si>
-  <si>
-    <t>(시행일 : 2024.8.1.)</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>06:56</t>
-  </si>
-  <si>
-    <t>07:06</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>07:36</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>07:16</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>08:03</t>
-  </si>
-  <si>
-    <t>08:24</t>
-  </si>
-  <si>
-    <t>[357-1번]  하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트-내도동-이호2동(대동마을)-제주민속오일시장 -월랑초등학교-한라병원-수협제주도지회-제주도청(신제주로터리)-세기아파트-보건소-(이도초등학교)-법원-제주중앙여자고등학교-아라초등학교-신성여자중고등학교-중앙고등학교-월평
-[358-1번]  하귀(수산)-하귀초등학교-하귀휴먼시아1,2단지-외도부영1,2차아파트-내도동-이호2동(대동마을)-제주민속오일시장-월랑초등학교-한라병원-수협제주도지회-제주도청(신제주로터리)-버스터미널-제주시청-제주중앙여자고등학교-아라초등학교-신성여자중고등학교-중앙고등학교-월평
-※ 토,공휴일,방학기간 운행 안함</t>
-  </si>
-  <si>
-    <t>수산(하귀)→제주도청→월평</t>
-  </si>
-  <si>
-    <t>삼영교통(064-713-7000)</t>
   </si>
 </sst>
 </file>
@@ -757,18 +757,17 @@
     <col min="11" max="11" width="14.0" customWidth="true"/>
     <col min="12" max="12" width="14.0" customWidth="true"/>
     <col min="13" max="13" width="14.0" customWidth="true"/>
-    <col min="14" max="14" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="1" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -777,11 +776,10 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="2" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -794,7 +792,6 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="1"/>
@@ -809,11 +806,10 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="5" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -824,11 +820,10 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5"/>
+      <c r="L5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -843,7 +838,6 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
-      <c r="N6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="8" t="s">
@@ -879,11 +873,8 @@
       <c r="L7" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="10" t="s">
         <v>11</v>
-      </c>
-      <c r="N7" s="10" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" ht="40.0" customHeight="true">
@@ -891,22 +882,22 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="E8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="F8" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="G8" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="H8" s="12" t="s">
         <v>17</v>
-      </c>
-      <c r="H8" s="12" t="s">
-        <v>15</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>18</v>
@@ -920,143 +911,55 @@
       <c r="L8" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="13" t="s">
+    </row>
+    <row r="9" ht="40.0" customHeight="true">
+      <c r="B9" s="14" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" ht="40.0" customHeight="true">
-      <c r="B9" s="11" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="D9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="12" t="s">
+      <c r="E9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="12" t="s">
+      <c r="F9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="G9" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="H9" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="I9" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="J9" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="L9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="40.0" customHeight="true">
-      <c r="B10" s="11" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" ht="40.0" customHeight="true">
-      <c r="B11" s="14" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" s="16" t="s">
-        <v>23</v>
+      <c r="M9" s="16" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:N4"/>
+    <mergeCell ref="F2:M4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:L6"/>
-    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="L5:M6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1079,11 +982,12 @@
     <col min="11" max="11" width="14.0" customWidth="true"/>
     <col min="12" max="12" width="14.0" customWidth="true"/>
     <col min="13" max="13" width="14.0" customWidth="true"/>
+    <col min="14" max="14" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="17" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C2" s="17"/>
       <c r="D2" s="17"/>
@@ -1098,6 +1002,7 @@
       <c r="K2" s="17"/>
       <c r="L2" s="17"/>
       <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="18" t="s">
@@ -1114,6 +1019,7 @@
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
       <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="17"/>
@@ -1128,6 +1034,7 @@
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
       <c r="M4" s="17"/>
+      <c r="N4" s="17"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="21" t="s">
@@ -1142,10 +1049,11 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5"/>
+      <c r="L5"/>
+      <c r="M5" s="23" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -1160,6 +1068,7 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
+      <c r="N6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="24" t="s">
@@ -1169,13 +1078,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>8</v>
@@ -1190,13 +1099,16 @@
         <v>5</v>
       </c>
       <c r="K7" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="M7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="26" t="s">
-        <v>12</v>
+      <c r="N7" s="26" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="40.0" customHeight="true">
@@ -1204,84 +1116,172 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="40.0" customHeight="true">
+      <c r="B9" s="27" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="28" t="s">
+      <c r="N9" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="40.0" customHeight="true">
+      <c r="B10" s="27" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="28" t="s">
+      <c r="E10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="28" t="s">
+      <c r="G10" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="28" t="s">
+      <c r="H10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="28" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="28" t="s">
+      <c r="J10" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="28" t="s">
+      <c r="K10" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="28" t="s">
+      <c r="L10" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M10" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="40.0" customHeight="true">
+      <c r="B11" s="30" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C11" s="31" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" ht="40.0" customHeight="true">
-      <c r="B9" s="30" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="31" t="s">
+      <c r="D11" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="31" t="s">
+      <c r="E11" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="31" t="s">
+      <c r="I11" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="31" t="s">
+      <c r="J11" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="31" t="s">
+      <c r="K11" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="31" t="s">
+      <c r="L11" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="31" t="s">
+      <c r="M11" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="32" t="s">
-        <v>23</v>
+      <c r="N11" s="32" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:M4"/>
+    <mergeCell ref="F2:N4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="B5:L6"/>
+    <mergeCell ref="M5:N6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1304,18 +1304,17 @@
     <col min="11" max="11" width="14.0" customWidth="true"/>
     <col min="12" max="12" width="14.0" customWidth="true"/>
     <col min="13" max="13" width="14.0" customWidth="true"/>
-    <col min="14" max="14" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="33" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
       <c r="E2" s="33"/>
       <c r="F2" s="35" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
@@ -1324,11 +1323,10 @@
       <c r="K2" s="33"/>
       <c r="L2" s="33"/>
       <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="34" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -1341,7 +1339,6 @@
       <c r="K3" s="33"/>
       <c r="L3" s="33"/>
       <c r="M3" s="33"/>
-      <c r="N3" s="33"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="33"/>
@@ -1356,11 +1353,10 @@
       <c r="K4" s="33"/>
       <c r="L4" s="33"/>
       <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="37" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C5"/>
       <c r="D5"/>
@@ -1371,11 +1367,10 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5"/>
-      <c r="M5" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5"/>
+      <c r="L5" s="39" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -1390,7 +1385,6 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
-      <c r="N6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="40" t="s">
@@ -1426,11 +1420,8 @@
       <c r="L7" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="M7" s="41" t="s">
+      <c r="M7" s="42" t="s">
         <v>11</v>
-      </c>
-      <c r="N7" s="42" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" ht="40.0" customHeight="true">
@@ -1438,22 +1429,22 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="E8" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="44" t="s">
+      <c r="F8" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="44" t="s">
+      <c r="G8" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="44" t="s">
+      <c r="H8" s="44" t="s">
         <v>17</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>15</v>
       </c>
       <c r="I8" s="44" t="s">
         <v>18</v>
@@ -1467,143 +1458,55 @@
       <c r="L8" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="44" t="s">
+      <c r="M8" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="45" t="s">
+    </row>
+    <row r="9" ht="40.0" customHeight="true">
+      <c r="B9" s="46" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" ht="40.0" customHeight="true">
-      <c r="B9" s="43" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="44" t="s">
+      <c r="D9" s="47" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="44" t="s">
+      <c r="E9" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="G9" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="H9" s="44" t="s">
+      <c r="F9" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="44" t="s">
+      <c r="G9" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="J9" s="44" t="s">
+      <c r="H9" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="44" t="s">
+      <c r="I9" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="L9" s="44" t="s">
+      <c r="J9" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="M9" s="44" t="s">
+      <c r="L9" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" ht="40.0" customHeight="true">
-      <c r="B10" s="43" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="C10" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="44" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="L10" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="M10" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="N10" s="45" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" ht="40.0" customHeight="true">
-      <c r="B11" s="46" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="C11" s="47" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="47" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="47" t="s">
-        <v>39</v>
-      </c>
-      <c r="I11" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="J11" s="47" t="s">
-        <v>41</v>
-      </c>
-      <c r="K11" s="47" t="s">
-        <v>42</v>
-      </c>
-      <c r="L11" s="47" t="s">
-        <v>43</v>
-      </c>
-      <c r="M11" s="47" t="s">
-        <v>44</v>
-      </c>
-      <c r="N11" s="48" t="s">
-        <v>23</v>
+      <c r="M9" s="48" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:N4"/>
+    <mergeCell ref="F2:M4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:L6"/>
-    <mergeCell ref="M5:N6"/>
+    <mergeCell ref="B5:K6"/>
+    <mergeCell ref="L5:M6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
@@ -1626,11 +1529,12 @@
     <col min="11" max="11" width="14.0" customWidth="true"/>
     <col min="12" max="12" width="14.0" customWidth="true"/>
     <col min="13" max="13" width="14.0" customWidth="true"/>
+    <col min="14" max="14" width="14.0" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="2" ht="100.0" customHeight="true">
       <c r="B2" s="49" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C2" s="49"/>
       <c r="D2" s="49"/>
@@ -1645,6 +1549,7 @@
       <c r="K2" s="49"/>
       <c r="L2" s="49"/>
       <c r="M2" s="49"/>
+      <c r="N2" s="49"/>
     </row>
     <row r="3" ht="25.0" customHeight="true">
       <c r="B3" s="50" t="s">
@@ -1661,6 +1566,7 @@
       <c r="K3" s="49"/>
       <c r="L3" s="49"/>
       <c r="M3" s="49"/>
+      <c r="N3" s="49"/>
     </row>
     <row r="4" ht="25.0" customHeight="true">
       <c r="B4" s="49"/>
@@ -1675,6 +1581,7 @@
       <c r="K4" s="49"/>
       <c r="L4" s="49"/>
       <c r="M4" s="49"/>
+      <c r="N4" s="49"/>
     </row>
     <row r="5" ht="25.0" customHeight="true">
       <c r="B5" s="53" t="s">
@@ -1689,10 +1596,11 @@
       <c r="I5"/>
       <c r="J5"/>
       <c r="K5"/>
-      <c r="L5" s="55" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5"/>
+      <c r="L5"/>
+      <c r="M5" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="N5"/>
     </row>
     <row r="6" ht="25.0" customHeight="true">
       <c r="B6"/>
@@ -1707,6 +1615,7 @@
       <c r="K6"/>
       <c r="L6"/>
       <c r="M6"/>
+      <c r="N6"/>
     </row>
     <row r="7" ht="40.0" customHeight="true">
       <c r="B7" s="56" t="s">
@@ -1716,13 +1625,13 @@
         <v>1</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="57" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" s="57" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="G7" s="57" t="s">
         <v>8</v>
@@ -1737,13 +1646,16 @@
         <v>5</v>
       </c>
       <c r="K7" s="57" t="s">
+        <v>4</v>
+      </c>
+      <c r="L7" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="57" t="s">
+      <c r="M7" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="M7" s="58" t="s">
-        <v>12</v>
+      <c r="N7" s="58" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8" ht="40.0" customHeight="true">
@@ -1751,84 +1663,172 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="60" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D8" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="J8" s="60" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" s="60" t="s">
+        <v>42</v>
+      </c>
+      <c r="L8" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="M8" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" ht="40.0" customHeight="true">
+      <c r="B9" s="59" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="C9" s="60" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="60" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="60" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" s="60" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="60" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="60" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="60" t="s">
+        <v>49</v>
+      </c>
+      <c r="M9" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="N9" s="61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" ht="40.0" customHeight="true">
+      <c r="B10" s="59" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="C10" s="60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="E10" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G10" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="60" t="s">
+      <c r="H10" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="60" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="J8" s="60" t="s">
+      <c r="J10" s="60" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="60" t="s">
+      <c r="K10" s="60" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="60" t="s">
+      <c r="L10" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M10" s="60" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="61" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" ht="40.0" customHeight="true">
+      <c r="B11" s="62" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" ht="40.0" customHeight="true">
-      <c r="B9" s="62" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="C9" s="63" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>58</v>
-      </c>
-      <c r="E9" s="63" t="s">
+      <c r="D11" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="63" t="s">
+      <c r="E11" s="63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="63" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="G9" s="63" t="s">
+      <c r="I11" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="H9" s="63" t="s">
+      <c r="J11" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="63" t="s">
+      <c r="K11" s="63" t="s">
         <v>62</v>
       </c>
-      <c r="J9" s="63" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" s="63" t="s">
+      <c r="L11" s="63" t="s">
         <v>63</v>
       </c>
-      <c r="L9" s="63" t="s">
+      <c r="M11" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="M9" s="64" t="s">
-        <v>23</v>
+      <c r="N11" s="64" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="B2:E2"/>
-    <mergeCell ref="F2:M4"/>
+    <mergeCell ref="F2:N4"/>
     <mergeCell ref="B3:E4"/>
-    <mergeCell ref="B5:K6"/>
-    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="B5:L6"/>
+    <mergeCell ref="M5:N6"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
